--- a/docs/test/unit/NOUS-103/観点表_consistencyChecker.xlsx
+++ b/docs/test/unit/NOUS-103/観点表_consistencyChecker.xlsx
@@ -13,9 +13,9 @@
     <sheet name="対象概要" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'観点表'!$A$4:$Q$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'観点表'!$A$4:$Q$32</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'観点表'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'テストデータ'!$A$4:$F$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'テストデータ'!$A$4:$F$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q31"/>
+  <dimension ref="A1:Q32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2489,12 +2489,12 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>TC-UT_CON-019</t>
+          <t>TC-UT_CON-020</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>splitSentences</t>
+          <t>checkConsistency</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -2504,36 +2504,40 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>同値分割</t>
+          <t>状態遷移</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>splitSentences は半角の ! ? でも切り、空の行は除く</t>
+          <t>C01：解除の後にフォローし直した相手への返信は候補にしない</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>前提：なし
-入力：一!二?\n\n三</t>
+          <t>前提：haruka の投稿、minato が 1 巡目に follow・2 巡目に unfollow・3 巡目に follow（継続中）
+入力：4 巡目に reply</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>[一!, 二?, 三]</t>
-        </is>
-      </c>
-      <c r="I31" s="5" t="inlineStr"/>
+          <t>空の配列（フォローし直した相手は「解除した相手」に当たらない）</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>B1-F, B2-F, B3-F</t>
+        </is>
+      </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>一時 DB（createTestDb、マイグレーション済み）。generationSeed で世界・エージェント・生成イベントを入れる</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr"/>
       <c r="L31" s="5" t="inlineStr"/>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>TC-UT_CON-019 splitSentences は半角の ! ? でも切り、空の行は除く</t>
+          <t>TC-UT_CON-020 C01：解除の後にフォローし直した相手への返信は候補にしない</t>
         </is>
       </c>
       <c r="N31" s="6" t="inlineStr">
@@ -2545,13 +2549,81 @@
       <c r="P31" s="6" t="inlineStr"/>
       <c r="Q31" s="7" t="inlineStr">
         <is>
+          <t>既存テスト：なし
+疑い：疑い 1：最後の解除から 3 巡以内なら、フォローし直した後でも C01 の候補にする
+2026-10-26 Kouhei Tajima さんの決定（NOUS-103）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>TC-UT_CON-019</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>splitSentences</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>正常系</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>同値分割</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>splitSentences は半角の ! ? でも切り、空の行は除く</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>前提：なし
+入力：一!二?\n\n三</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>[一!, 二?, 三]</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr"/>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr"/>
+      <c r="L32" s="5" t="inlineStr"/>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>TC-UT_CON-019 splitSentences は半角の ! ? でも切り、空の行は除く</t>
+        </is>
+      </c>
+      <c r="N32" s="6" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
+      <c r="O32" s="6" t="inlineStr"/>
+      <c r="P32" s="6" t="inlineStr"/>
+      <c r="Q32" s="7" t="inlineStr">
+        <is>
           <t>既存テスト：一部 TC-NOUS62_DEV-48（全角の句点だけ）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:Q31"/>
-  <conditionalFormatting sqref="A5:Q81">
+  <autoFilter ref="A4:Q32"/>
+  <conditionalFormatting sqref="A5:Q82">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$N5="NG"</formula>
     </cfRule>
@@ -2563,10 +2635,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="N5:N81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N5:N82" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未実施,OK,NG,保留,対象外"</formula1>
     </dataValidation>
-    <dataValidation sqref="D5:D81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D5:D82" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"正常系,異常系"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2581,7 +2653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2618,7 +2690,7 @@
         </is>
       </c>
       <c r="B5" s="10">
-        <f>COUNTA(観点表!$B$5:$B$81)</f>
+        <f>COUNTA(観点表!$B$5:$B$82)</f>
         <v/>
       </c>
     </row>
@@ -2629,7 +2701,7 @@
         </is>
       </c>
       <c r="B6" s="10">
-        <f>COUNTIF(観点表!$D$5:$D$81,"正常系")</f>
+        <f>COUNTIF(観点表!$D$5:$D$82,"正常系")</f>
         <v/>
       </c>
     </row>
@@ -2640,7 +2712,7 @@
         </is>
       </c>
       <c r="B7" s="10">
-        <f>COUNTIF(観点表!$D$5:$D$81,"異常系")</f>
+        <f>COUNTIF(観点表!$D$5:$D$82,"異常系")</f>
         <v/>
       </c>
     </row>
@@ -2660,7 +2732,7 @@
         </is>
       </c>
       <c r="B10" s="10">
-        <f>COUNTIF(観点表!$E$5:$E$81,"分岐網羅")</f>
+        <f>COUNTIF(観点表!$E$5:$E$82,"分岐網羅")</f>
         <v/>
       </c>
     </row>
@@ -2671,7 +2743,7 @@
         </is>
       </c>
       <c r="B11" s="10">
-        <f>COUNTIF(観点表!$E$5:$E$81,"同値分割")</f>
+        <f>COUNTIF(観点表!$E$5:$E$82,"同値分割")</f>
         <v/>
       </c>
     </row>
@@ -2682,135 +2754,146 @@
         </is>
       </c>
       <c r="B12" s="10">
-        <f>COUNTIF(観点表!$E$5:$E$81,"境界値")</f>
+        <f>COUNTIF(観点表!$E$5:$E$82,"境界値")</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
+          <t>状態遷移</t>
+        </is>
+      </c>
+      <c r="B13" s="10">
+        <f>COUNTIF(観点表!$E$5:$E$82,"状態遷移")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
           <t>開発者テスト</t>
         </is>
       </c>
-      <c r="B13" s="10">
-        <f>COUNTIF(観点表!$E$5:$E$81,"開発者テスト")</f>
+      <c r="B14" s="10">
+        <f>COUNTIF(観点表!$E$5:$E$82,"開発者テスト")</f>
         <v/>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>テストデータ</t>
         </is>
       </c>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="9" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>作成済み</t>
-        </is>
-      </c>
-      <c r="B16" s="10">
-        <f>COUNTIF(観点表!$K$5:$K$81,"?*")</f>
-        <v/>
-      </c>
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="9" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
+          <t>作成済み</t>
+        </is>
+      </c>
+      <c r="B17" s="10">
+        <f>COUNTIF(観点表!$K$5:$K$82,"?*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
           <t>未作成</t>
         </is>
       </c>
-      <c r="B17" s="10">
-        <f>B5-B16</f>
+      <c r="B18" s="10">
+        <f>B5-B17</f>
         <v/>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>実施状況</t>
         </is>
       </c>
-      <c r="B19" s="9" t="n"/>
-      <c r="C19" s="9" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="B20" s="10">
-        <f>COUNTIF(観点表!$N$5:$N$81,"未実施")</f>
-        <v/>
-      </c>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>未実施</t>
         </is>
       </c>
       <c r="B21" s="10">
-        <f>COUNTIF(観点表!$N$5:$N$81,"OK")</f>
+        <f>COUNTIF(観点表!$N$5:$N$82,"未実施")</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>NG</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="B22" s="10">
-        <f>COUNTIF(観点表!$N$5:$N$81,"NG")</f>
+        <f>COUNTIF(観点表!$N$5:$N$82,"OK")</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>NG</t>
         </is>
       </c>
       <c r="B23" s="10">
-        <f>COUNTIF(観点表!$N$5:$N$81,"保留")</f>
+        <f>COUNTIF(観点表!$N$5:$N$82,"NG")</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>対象外</t>
+          <t>保留</t>
         </is>
       </c>
       <c r="B24" s="10">
-        <f>COUNTIF(観点表!$N$5:$N$81,"対象外")</f>
+        <f>COUNTIF(観点表!$N$5:$N$82,"保留")</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>消化率（未実施以外 / 総数）</t>
-        </is>
-      </c>
-      <c r="B25" s="11">
-        <f>IF(B5=0,0,(B5-B20)/B5)</f>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="B25" s="10">
+        <f>COUNTIF(観点表!$N$5:$N$82,"対象外")</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
+          <t>消化率（未実施以外 / 総数）</t>
+        </is>
+      </c>
+      <c r="B26" s="11">
+        <f>IF(B5=0,0,(B5-B21)/B5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
           <t>合格率（OK / (総数-対象外)）</t>
         </is>
       </c>
-      <c r="B26" s="11">
-        <f>IF(B5-B24=0,0,B21/(B5-B24))</f>
+      <c r="B27" s="11">
+        <f>IF(B5-B25=0,0,B22/(B5-B25))</f>
         <v/>
       </c>
     </row>
@@ -2825,7 +2908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3405,12 +3488,12 @@
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
         <is>
-          <t>TC-UT_CON-019</t>
+          <t>TC-UT_CON-020</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>splitSentences は半角の ! ? でも切り、空の行は除く</t>
+          <t>C01：解除の後にフォローし直した相手への返信は候補にしない</t>
         </is>
       </c>
       <c r="C31" s="13" t="inlineStr">
@@ -3422,8 +3505,28 @@
       <c r="E31" s="13" t="inlineStr"/>
       <c r="F31" s="13" t="inlineStr"/>
     </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>TC-UT_CON-019</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>splitSentences は半角の ! ? でも切り、空の行は除く</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>未作成</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="inlineStr"/>
+      <c r="E32" s="13" t="inlineStr"/>
+      <c r="F32" s="13" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:F31"/>
+  <autoFilter ref="A4:F32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -3719,7 +3822,7 @@
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="18" t="inlineStr">
         <is>
-          <t>・確認事項 1：C01 は、解除の後にフォローし直した相手への返信も、最後の解除から 3 巡以内なら候補にする。9章の文言どおりだが、フォローし直した後の返信を矛盾とみなすかは確認したい。</t>
+          <t>・疑い 1：C01 は、解除の後にフォローし直した相手への返信も、最後の解除から 3 巡以内なら候補にする（TC-UT_CON-020）。2026-10-26 に Kouhei Tajima さんが、フォローし直した相手は「解除した相手」に当たらず矛盾としないと決めた。</t>
         </is>
       </c>
     </row>
